--- a/reports/Debug-snowbowl-20260105/Month to Date (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20260105/Month to Date (Prior Year)_Revenue.xlsx
@@ -58,13 +58,13 @@
     <t>account</t>
   </si>
   <si>
+    <t>T100</t>
+  </si>
+  <si>
     <t>T101</t>
   </si>
   <si>
     <t>T103</t>
-  </si>
-  <si>
-    <t>T100</t>
   </si>
   <si>
     <t>department</t>
@@ -469,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -493,11 +493,17 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="D2" s="2">
-        <v>2104.80</v>
+        <v>408862.68</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -505,13 +511,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="2">
-        <v>410342.34</v>
+        <v>3483.63</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -519,159 +525,145 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="2">
-        <v>30967.47</v>
+        <v>16721.74</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2">
-        <v>819160.58</v>
+        <v>127393.68</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2">
-        <v>148654.68</v>
+        <v>243398.76</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2">
-        <v>245738.76</v>
+        <v>4058.04</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2">
-        <v>4058.04</v>
+        <v>62894.60</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2">
-        <v>65345.49</v>
+        <v>61.26</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="2">
-        <v>61.26</v>
+        <v>49104.47</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2">
-        <v>49104.47</v>
+        <v>99210.27</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" s="2">
-        <v>99210.27</v>
+        <v>5790.43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D13" s="2">
-        <v>5790.43</v>
+        <v>10597.52</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2">
-        <v>10597.52</v>
+        <v>23807.43</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="2">
-        <v>23807.43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="2">
-        <v>180.00</v>
+        <v>90.00</v>
       </c>
     </row>
   </sheetData>
